--- a/backlog/backlog.xlsx
+++ b/backlog/backlog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$F$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Backlog'!$A$1:$G$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +175,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normálna" xfId="0" builtinId="0"/>
@@ -257,7 +260,7 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Task hours are example estimates for one developer. Epic / Feature / User Story hours are SUMIFS roll-ups of their tasks.</t>
       </text>
@@ -555,15 +558,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,12 +591,17 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Estimated Hours</t>
         </is>
@@ -619,9 +628,10 @@
           <t>Middleware between an upstream system and KUKA AMR Fleet Manager: dispatch/cancel missions, sync mission and robot states, web UI.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="6">
-        <f>SUMIFS(F3:F64,B3:B64,"Task")</f>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="6">
+        <f>SUMIFS(G3:G64,B3:B64,"Task")</f>
         <v/>
       </c>
     </row>
@@ -646,9 +656,16 @@
           <t>Dispatching, cancelling and monitoring missions created by the middleware (UC1–UC5).</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="11">
-        <f>SUMIFS(F4:F30,B4:B30,"Task")</f>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>• Missions can be dispatched, cancelled and monitored through the middleware without using the KUKA FM UI
+• Only missions dispatched by the middleware are tracked, each with current status and full status history
+• All user operations and KUKA calls are logged in Seq</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="11">
+        <f>SUMIFS(G4:G30,B4:B30,"Task")</f>
         <v/>
       </c>
     </row>
@@ -673,9 +690,17 @@
           <t>As an operator I want to dispatch a new RACK_MOVE mission to a selected robot.</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n"/>
-      <c r="F4" s="16">
-        <f>SUMIFS(F5:F9,B5:B9,"Task")</f>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>• Dialog requires a robot from the DB, start node, target node, container code and priority 1–99
+• Invalid input is rejected with 400 and no KUKA call is made
+• On KUKA success the mission is stored with status 10 (Created) and appears in the list
+• On KUKA error an error is shown (502), nothing is stored and the error is logged</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="16">
+        <f>SUMIFS(G5:G9,B5:B9,"Task")</f>
         <v/>
       </c>
     </row>
@@ -700,12 +725,13 @@
           <t>Create POST /api/missions. Validate start node, target node, container code, priority (1–99) and that the robot exists. Return 201 or a validation error.</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="G5" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -730,12 +756,13 @@
           <t>Persist the new mission with status 10 (Created), generated mission_code/request_id and robot FK. Write only after KUKA FM confirms success.</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="20" t="n"/>
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="G6" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -760,12 +787,13 @@
           <t>Call submitMission at https://kukafm.its.fei with Authorization token. Build RACK_MOVE body (missionData start/target node, robotIds); other params from appsettings. Handle success=false.</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="20" t="n"/>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="G7" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -790,12 +818,13 @@
           <t>Dialog opened by '+ Dispatch mission' with robot select (robots from DB), start/target node, container code and priority. Show success or error message.</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="G8" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -820,12 +849,13 @@
           <t>Unit tests for input validation, KUKA submitMission request mapping and service logic (KUKA client and DB mocked).</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="20" t="n"/>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="G9" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -850,9 +880,17 @@
           <t>As an operator I want to force-cancel a running mission.</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="16">
-        <f>SUMIFS(F11:F15,B11:B15,"Task")</f>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>• Cancel is offered only for active missions (10, 20, 25, 28, 50) and needs confirmation
+• missionCancel is sent with FORCE
+• Unknown mission returns 404, non-active mission returns 409
+• Final status Cancelled (31) appears after the next sync</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="16">
+        <f>SUMIFS(G11:G15,B11:B15,"Task")</f>
         <v/>
       </c>
     </row>
@@ -877,12 +915,13 @@
           <t>Create POST /api/missions/{code}/cancel. Return 200 on success, 404 if not found, 409 if mission is not active.</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="20" t="n"/>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="G11" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -907,12 +946,13 @@
           <t>Load mission by mission_code and check that its status is active (10, 20, 25, 28, 50).</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="G12" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -937,12 +977,13 @@
           <t>Call missionCancel with missionCode and cancelMode FORCE. Final status (31 Cancelled) is stored later by mission sync.</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="G13" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -967,12 +1008,13 @@
           <t>Cancel button shown only on active missions; confirmation dialog mentioning FORCE cancel; show result message.</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="G14" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -997,12 +1039,13 @@
           <t>Unit tests for active / not-active / not-found cases and KUKA FM error handling (KUKA client and DB mocked).</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="G15" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1027,9 +1070,16 @@
           <t>As an operator I want to see the current status of active and finished missions.</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="16">
-        <f>SUMIFS(F17:F20,B17:B20,"Task")</f>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>• List shows code, status, robot, nodes, container, priority and times
+• All / Active / Finished filter works
+• Data refreshes every 1 s while Auto-refresh is on</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="16">
+        <f>SUMIFS(G17:G20,B17:B20,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1054,12 +1104,13 @@
           <t>Create GET /api/missions with optional filter state=active|finished; return missions with status code and name, robot and timestamps.</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="G17" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1084,12 +1135,13 @@
           <t>EF Core query over mission table with status filter, robot join and ordering by created_at desc.</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="G18" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1114,12 +1166,13 @@
           <t>Missions table (code, status badge, robot, nodes, container, priority, times) with All/Active/Finished filter and auto-refresh every 1 s.</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="G19" s="21" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1144,12 +1197,13 @@
           <t>Unit tests for the active/finished filter logic and the missions service.</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="G20" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1174,9 +1228,15 @@
           <t>As an operator I want to see all previous statuses of a mission.</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="16">
-        <f>SUMIFS(F22:F25,B22:B25,"Task")</f>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>• Show history shows all previous states, newest first, with valid-from and valid-to times
+• Unknown mission returns 404</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="16">
+        <f>SUMIFS(G22:G25,B22:B25,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1201,12 +1261,13 @@
           <t>Create GET /api/missions/{code}/history returning previous states (status, robot, valid_from, valid_to).</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="G22" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1231,12 +1292,13 @@
           <t>Query mission_status_history by mission_id ordered by valid_to desc.</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="20" t="n"/>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="G23" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1261,12 +1323,13 @@
           <t>'Show history' checkbox adds grey previous-state rows under each mission.</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="G24" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1291,12 +1354,13 @@
           <t>Unit tests for the mission history service (existing/unknown mission).</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="G25" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1321,9 +1385,17 @@
           <t>As the system I want to periodically sync statuses of tracked missions from KUKA FM.</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="16">
-        <f>SUMIFS(F27:F30,B27:B30,"Task")</f>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>• Starts only after the first robot sync
+• One jobQuery per tick plus per-jobCode fallback for missing missions
+• Every change stores the previous state in history; a final status sets completed_at and the mission is no longer polled
+• KUKA errors are logged, nothing is written and the next tick retries</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="16">
+        <f>SUMIFS(G27:G30,B27:B30,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1348,12 +1420,13 @@
           <t>Hosted background service running on interval from appsettings; starts only after first robot sync finished; logs to Seq.</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="G27" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1378,12 +1451,13 @@
           <t>For each changed mission copy previous state into mission_status_history, update status/robot/updated_at; set completed_at for final statuses.</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="G28" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1408,12 +1482,13 @@
           <t>Call jobQuery once per tick (limit and filters from appsettings) and match results to active missions by jobCode.</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="G29" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1438,12 +1513,13 @@
           <t>Unit tests for sync logic: status change, no change, final status, unknown jobCode and KUKA FM error.</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="G30" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1468,9 +1544,15 @@
           <t>Monitoring robots and their states synchronized from KUKA FM (UC6–UC8).</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="11">
-        <f>SUMIFS(F32:F46,B32:B46,"Task")</f>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>• All robots from KUKA FM are synced periodically with current state and full history
+• UI shows robots with mapped state Available / Busy / Offline</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="11">
+        <f>SUMIFS(G32:G46,B32:B46,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1495,9 +1577,16 @@
           <t>As an operator I want to see all robots and their current state.</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="16">
-        <f>SUMIFS(F33:F36,B33:B36,"Task")</f>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>• List shows code, type, state badge, KUKA status, battery, map, node, mission and updated time
+• State mapping: Idle → Available; Departure, Executing, Charging, Updating → Busy; Offline, Abnormal → Offline
+• Data refreshes every 1 s while Auto-refresh is on</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="16">
+        <f>SUMIFS(G33:G36,B33:B36,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1522,12 +1611,13 @@
           <t>Create GET /api/robots returning robots with KUKA status and mapped state (Idle→Available; Departure/Executing/Charging/Updating→Busy; Offline/Abnormal→Offline).</t>
         </is>
       </c>
-      <c r="E33" s="17" t="inlineStr">
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="G33" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1552,12 +1642,13 @@
           <t>EF Core query over robot table ordered by robot_code.</t>
         </is>
       </c>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="G34" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1582,12 +1673,13 @@
           <t>Robots table (code, type, state badge, KUKA status, battery bar, map, node, mission, updated) with auto-refresh every 1 s.</t>
         </is>
       </c>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="G35" s="21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1612,12 +1704,13 @@
           <t>Unit tests for status mapping (Available/Busy/Offline) and the robots service.</t>
         </is>
       </c>
-      <c r="E36" s="17" t="inlineStr">
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="G36" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1642,9 +1735,15 @@
           <t>As an operator I want to see all previous states of a robot.</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="16">
-        <f>SUMIFS(F38:F41,B38:B41,"Task")</f>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>• Show history shows previous states, newest first, with valid-from and valid-to times
+• Unknown robot returns 404</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="16">
+        <f>SUMIFS(G38:G41,B38:B41,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1669,12 +1768,13 @@
           <t>Create GET /api/robots/{id}/history returning previous states with valid_from/valid_to.</t>
         </is>
       </c>
-      <c r="E38" s="17" t="inlineStr">
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="G38" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1699,12 +1799,13 @@
           <t>Query robot_status_history by robot_id ordered by valid_to desc.</t>
         </is>
       </c>
-      <c r="E39" s="17" t="inlineStr">
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="G39" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1729,12 +1830,13 @@
           <t>'Show history' checkbox adds grey previous-state rows under each robot.</t>
         </is>
       </c>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="G40" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1759,12 +1861,13 @@
           <t>Unit tests for the robot history service (existing/unknown robot).</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F41" s="21" t="n">
+      <c r="G41" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1789,9 +1892,18 @@
           <t>As the system I want to periodically sync all robots from KUKA FM.</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="16">
-        <f>SUMIFS(F43:F46,B43:B46,"Task")</f>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>• Runs first on startup, then on the configured interval
+• New robots are inserted
+• Any change stores the previous state in history, then updates the robot
+• KUKA errors are logged, nothing is written and the next tick retries
+• The token is never logged</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="16">
+        <f>SUMIFS(G43:G46,B43:B46,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1816,12 +1928,13 @@
           <t>Hosted background service on interval from appsettings; runs first on startup and signals mission sync to start.</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F43" s="21" t="n">
+      <c r="G43" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1846,12 +1959,13 @@
           <t>Insert new robots; for every changed robot copy previous state into robot_status_history and update current values.</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F44" s="21" t="n">
+      <c r="G44" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1876,12 +1990,13 @@
           <t>Call robotQuery without filters to get all robots; map response fields to robot entity.</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F45" s="21" t="n">
+      <c r="G45" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1906,12 +2021,13 @@
           <t>Unit tests for sync logic: new robot, changed robot, unchanged robot and KUKA FM error.</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="F46" s="21" t="n">
+      <c r="G46" s="21" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1936,9 +2052,14 @@
           <t>Containerization, CI and CD of the whole application on the local Azure DevOps Windows agent with Docker Desktop.</t>
         </is>
       </c>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="11">
-        <f>SUMIFS(F48:F64,B48:B64,"Task")</f>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>• Application runs fully in Docker and is built, checked and deployed by Azure DevOps pipelines without manual file edits</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="11">
+        <f>SUMIFS(G48:G64,B48:B64,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1963,9 +2084,16 @@
           <t>As a team we want the application to run fully in Docker containers.</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="16">
-        <f>SUMIFS(F49:F53,B49:B53,"Task")</f>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>• docker compose up --build starts web (8080), api (internal only), postgres (5432) and seq (5341)
+• UI and /api work through nginx
+• Dev and prod use separate volumes</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="16">
+        <f>SUMIFS(G49:G53,B49:B53,"Task")</f>
         <v/>
       </c>
     </row>
@@ -1990,12 +2118,13 @@
           <t>Multi-stage Dockerfile: build and publish with .NET SDK image, run on ASP.NET runtime image.</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F49" s="21" t="n">
+      <c r="G49" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2020,12 +2149,13 @@
           <t>Multi-stage Dockerfile: build Angular app with Node image, serve static files from nginx image.</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E50" s="20" t="n"/>
+      <c r="F50" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F50" s="21" t="n">
+      <c r="G50" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2050,12 +2180,13 @@
           <t>nginx.conf serving SPA with fallback to index.html and reverse proxy /api to the backend container.</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E51" s="20" t="n"/>
+      <c r="F51" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F51" s="21" t="n">
+      <c r="G51" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2080,12 +2211,13 @@
           <t>Compose file with web (8080), api (internal only), postgres (5432) and seq (5341) with persistent volumes; images always built.</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E52" s="20" t="n"/>
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F52" s="21" t="n">
+      <c r="G52" s="21" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2110,12 +2242,13 @@
           <t>appsettings.Development.json with root/password DB credentials; Production values injected by the pipeline.</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr">
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F53" s="21" t="n">
+      <c r="G53" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2140,9 +2273,16 @@
           <t>As a team we want every change built, checked and tested automatically.</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n"/>
-      <c r="F54" s="16">
-        <f>SUMIFS(F55:F58,B55:B58,"Task")</f>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>• Manual run builds backend and frontend
+• Run fails on vulnerable NuGet packages, high/critical npm audit findings or failing unit tests
+• Test results are published</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n"/>
+      <c r="G54" s="16">
+        <f>SUMIFS(G55:G58,B55:B58,"Task")</f>
         <v/>
       </c>
     </row>
@@ -2167,12 +2307,13 @@
           <t>Azure Pipelines YAML building backend and frontend; agent pool and name taken from pipeline variables.</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F55" s="21" t="n">
+      <c r="G55" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2197,12 +2338,13 @@
           <t>Fail the build when vulnerable NuGet packages are found.</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F56" s="21" t="n">
+      <c r="G56" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2227,12 +2369,13 @@
           <t>Run npm audit on the frontend and fail on high/critical vulnerabilities.</t>
         </is>
       </c>
-      <c r="E57" s="17" t="inlineStr">
+      <c r="E57" s="20" t="n"/>
+      <c r="F57" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F57" s="21" t="n">
+      <c r="G57" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2257,12 +2400,13 @@
           <t>Run dotnet test for backend unit tests and publish test results to the pipeline.</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F58" s="21" t="n">
+      <c r="G58" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2287,9 +2431,17 @@
           <t>As a team we want successful builds deployed automatically to local Docker.</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="16">
-        <f>SUMIFS(F60:F64,B60:B64,"Task")</f>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>• Manual run only
+• Placeholders are replaced from secret variables before any docker command; secrets never appear in logs or the repo
+• Smoke check passes for :8080 and /api/health
+• Migrations are applied on API startup</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n"/>
+      <c r="G59" s="16">
+        <f>SUMIFS(G60:G64,B60:B64,"Task")</f>
         <v/>
       </c>
     </row>
@@ -2314,12 +2466,13 @@
           <t>Azure Pipelines YAML used for deployment. Manual run only (trigger: none).</t>
         </is>
       </c>
-      <c r="E60" s="17" t="inlineStr">
+      <c r="E60" s="20" t="n"/>
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F60" s="21" t="n">
+      <c r="G60" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2344,12 +2497,13 @@
           <t>Create appsettings.Production.json from secret pipeline variables (KUKA FM token, DB credentials).</t>
         </is>
       </c>
-      <c r="E61" s="17" t="inlineStr">
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F61" s="21" t="n">
+      <c r="G61" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2374,12 +2528,13 @@
           <t>Run docker compose build and up -d on the agent host's Docker Desktop (Linux containers). Include docker builder prune -af to cleanup used resources.</t>
         </is>
       </c>
-      <c r="E62" s="17" t="inlineStr">
+      <c r="E62" s="20" t="n"/>
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F62" s="21" t="n">
+      <c r="G62" s="21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2404,12 +2559,13 @@
           <t>API applies EF Core migrations on startup (Database.Migrate()) so every deployment updates the PostgreSQL schema; no migration step in the pipeline.</t>
         </is>
       </c>
-      <c r="E63" s="17" t="inlineStr">
+      <c r="E63" s="20" t="n"/>
+      <c r="F63" s="17" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="F63" s="21" t="n">
+      <c r="G63" s="21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2434,17 +2590,18 @@
           <t>After deploy verify that the frontend (8080) and /api through nginx respond; fail the pipeline otherwise.</t>
         </is>
       </c>
-      <c r="E64" s="17" t="inlineStr">
+      <c r="E64" s="20" t="n"/>
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="F64" s="21" t="n">
+      <c r="G64" s="21" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F64"/>
+  <autoFilter ref="A1:G64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2490,7 +2647,7 @@
         </is>
       </c>
       <c r="B3" s="23">
-        <f>Backlog!F3</f>
+        <f>Backlog!G3</f>
         <v/>
       </c>
     </row>
@@ -2501,7 +2658,7 @@
         </is>
       </c>
       <c r="B4" s="23">
-        <f>Backlog!F31</f>
+        <f>Backlog!G31</f>
         <v/>
       </c>
     </row>
@@ -2512,7 +2669,7 @@
         </is>
       </c>
       <c r="B5" s="23">
-        <f>Backlog!F47</f>
+        <f>Backlog!G47</f>
         <v/>
       </c>
     </row>
@@ -2558,7 +2715,7 @@
         </is>
       </c>
       <c r="B10" s="23">
-        <f>SUMIFS(Backlog!F:F,Backlog!E:E,"Backend",Backlog!B:B,"Task")</f>
+        <f>SUMIFS(Backlog!G:G,Backlog!F:F,"Backend",Backlog!B:B,"Task")</f>
         <v/>
       </c>
     </row>
@@ -2569,7 +2726,7 @@
         </is>
       </c>
       <c r="B11" s="23">
-        <f>SUMIFS(Backlog!F:F,Backlog!E:E,"Frontend",Backlog!B:B,"Task")</f>
+        <f>SUMIFS(Backlog!G:G,Backlog!F:F,"Frontend",Backlog!B:B,"Task")</f>
         <v/>
       </c>
     </row>
@@ -2580,7 +2737,7 @@
         </is>
       </c>
       <c r="B12" s="23">
-        <f>SUMIFS(Backlog!F:F,Backlog!E:E,"Testing",Backlog!B:B,"Task")</f>
+        <f>SUMIFS(Backlog!G:G,Backlog!F:F,"Testing",Backlog!B:B,"Task")</f>
         <v/>
       </c>
     </row>
@@ -2591,7 +2748,7 @@
         </is>
       </c>
       <c r="B13" s="23">
-        <f>SUMIFS(Backlog!F:F,Backlog!E:E,"Deployment",Backlog!B:B,"Task")</f>
+        <f>SUMIFS(Backlog!G:G,Backlog!F:F,"Deployment",Backlog!B:B,"Task")</f>
         <v/>
       </c>
     </row>
